--- a/backend/test_codes/table_analyzer_codes/outputs2/e30214c2-bb28-4650-8ef0-43c2c27cc0b5_039_reconstructed.xlsx
+++ b/backend/test_codes/table_analyzer_codes/outputs2/e30214c2-bb28-4650-8ef0-43c2c27cc0b5_039_reconstructed.xlsx
@@ -437,28 +437,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>行标记</t>
         </is>
@@ -467,185 +477,227 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;(人民币百万元,百分比除外)</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>2024年第四季度</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>折算前数值</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>折算后数值</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>2</v>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;10&gt;&gt;其他项目</t>
+          <t>10&gt;&gt;其他项目</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>其他项目</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>2,166,218</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>278,418</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;11&gt;&gt;其中:与衍生工具及其他抵(质)押品要求 相关的现金流出</t>
+          <t>11&gt;&gt;其中:与衍生工具及其他抵(质)押品要求相关的现金流出</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>其中:与衍生工具及其他抵(质)押品要求 相关的现金流出</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>75,603</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>75,603</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;12&gt;&gt;其中:与抵(质)押债务工具融资流失相关 的现金流出</t>
+          <t>12&gt;&gt;其中:与抵(质)押债务工具融资流失相关的现金流出</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>其中:与抵(质)押债务工具融资流失相关 的现金流出</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>7,133</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>7,133</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;13&gt;&gt;其中:信用便利和流动性便利</t>
+          <t>13&gt;&gt;其中:信用便利和流动性便利</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>其中:信用便利和流动性便利</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>2,083,482</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>195,682</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
+      <c r="E8" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;14&gt;&gt;其他契约性融资义务</t>
+          <t>14&gt;&gt;其他契约性融资义务</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>其他契约性融资义务</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>5,239</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>5,220</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;15&gt;&gt;或有融资义务</t>
+          <t>15&gt;&gt;或有融资义务</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>或有融资义务</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>6,033,921</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>725.646</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;16&gt;&gt;预期现金流出总量</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
+          <t>16&gt;&gt;预期现金流出总量</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>预期现金流出总量</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>7,516,892</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
+      <c r="E11" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -656,148 +708,185 @@
       </c>
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>现金流入&gt;&gt;序号&gt;&gt;17&gt;&gt;抵(质)押借贷(包括逆回购和借入证券)</t>
+          <t>现金流入&gt;&gt;17&gt;&gt;抵(质)押借贷(包括逆回购和借入证券)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>抵(质)押借贷(包括逆回购和借入证券)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
           <t>1,062,976</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>1,062.976</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>现金流入&gt;&gt;序号&gt;&gt;18&gt;&gt;完全正常履约付款带来的现金流入</t>
+          <t>现金流入&gt;&gt;18&gt;&gt;完全正常履约付款带来的现金流入</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>完全正常履约付款带来的现金流入</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t>2.432,106</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>1.420,346</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
+      <c r="E14" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>现金流入&gt;&gt;序号&gt;&gt;19&gt;&gt;其他现金流入</t>
+          <t>现金流入&gt;&gt;19&gt;&gt;其他现金流入</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>其他现金流入</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
           <t>80.804</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>75.837</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>现金流入&gt;&gt;序号&gt;&gt;20&gt;&gt;预期现金流入总量</t>
+          <t>现金流入&gt;&gt;20&gt;&gt;预期现金流入总量</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>预期现金流入总量</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
           <t>3,575,886</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>2,559,159</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>调整后数值</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;21&gt;&gt;合格优质流动性资产</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr"/>
-      <c r="C18" s="3" t="inlineStr">
+          <t>21&gt;&gt;合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>6,237,408</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;22&gt;&gt;现金净流出量</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="3" t="inlineStr">
+          <t>22&gt;&gt;现金净流出量</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>现金净流出量</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>4,957,733</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>0</v>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;23&gt;&gt;流动性覆盖率(%)1</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="inlineStr">
+          <t>23&gt;&gt;流动性覆盖率(%)1</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>流动性覆盖率(%)1</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>125.73</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -813,6 +902,9 @@
         <v>1</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>2</v>
       </c>
     </row>
